--- a/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
+++ b/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m-takizawa\git\lms-test-src-rp2-takizawa\test_code_creation_name\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0836DF-AA68-4666-BBA5-E122EEAD1DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D055EE-B81C-4C65-9B87-F65703BE0AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="902" xr2:uid="{44B375E4-2A13-4BCF-8037-AC3B45EA62FC}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="90">
   <si>
     <t>関係者外秘</t>
   </si>
@@ -1288,6 +1288,17 @@
   </si>
   <si>
     <t>Case01・Case02 レビュー指摘対応、テストコード修正</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>作成</t>
+    <rPh sb="0" eb="2">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Case03・Case04 レビュー指摘対応、テストコード修正</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -2285,18 +2296,30 @@
         <v>64</v>
       </c>
       <c r="D23" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="19.5">
+      <c r="B24" s="9">
+        <v>46283</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="19.5">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-    </row>
     <row r="25" spans="2:4" ht="19.5">
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="B25" s="9">
+        <v>46283</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="26" spans="2:4" ht="19.5">
       <c r="B26" s="13"/>

--- a/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
+++ b/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m-takizawa\git\lms-test-src-rp2-takizawa\test_code_creation_name\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D055EE-B81C-4C65-9B87-F65703BE0AB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5395F5-7107-4F0C-8FE9-9D44826C8455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="902" xr2:uid="{44B375E4-2A13-4BCF-8037-AC3B45EA62FC}"/>
   </bookViews>
@@ -153,7 +153,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>関係者外秘</t>
   </si>
@@ -1299,6 +1299,20 @@
   </si>
   <si>
     <t>Case03・Case04 レビュー指摘対応、テストコード修正</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>瀧澤</t>
+    <rPh sb="0" eb="2">
+      <t>タキザワ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>Case05・Case06 作成</t>
+    <rPh sb="14" eb="16">
+      <t>サクセイ</t>
+    </rPh>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1515,7 +1529,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1636,6 +1650,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1648,7 +1675,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1802,6 +1829,15 @@
     </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2311,20 +2347,26 @@
       </c>
     </row>
     <row r="25" spans="2:4" ht="19.5">
-      <c r="B25" s="9">
+      <c r="B25" s="52">
         <v>46283</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="53" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="53" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="19.5">
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
+      <c r="B26" s="52">
+        <v>46283</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="54" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="27" spans="2:4" ht="19.5">
       <c r="B27" s="13"/>

--- a/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
+++ b/test_code_creation_name/doc/RP2_10_結合テスト仕様書_TakizawaMunehiro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m-takizawa\git\lms-test-src-rp2-takizawa\test_code_creation_name\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5395F5-7107-4F0C-8FE9-9D44826C8455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C360C7-316F-4797-85EF-098ABC105B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="902" xr2:uid="{44B375E4-2A13-4BCF-8037-AC3B45EA62FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="902" xr2:uid="{44B375E4-2A13-4BCF-8037-AC3B45EA62FC}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -1675,7 +1675,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1838,6 +1838,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2358,7 +2361,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="19.5">
-      <c r="B26" s="52">
+      <c r="B26" s="55">
         <v>46283</v>
       </c>
       <c r="C26" s="54" t="s">
